--- a/RAGU LOS/all_lobs/output/frn_subgroup_ragu.xlsx
+++ b/RAGU LOS/all_lobs/output/frn_subgroup_ragu.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed.ali\ragu-los\RAGU LOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed.ali\ragu-los\RAGU LOS\all_lobs\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7227C7B-7EE4-43EB-81D8-A46C4E3E0965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D5F0D7-74FE-48F3-843B-8A6168A94C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23715" yWindow="-21885" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23820" yWindow="-21720" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Tables (Q)" sheetId="1" r:id="rId1"/>
+    <sheet name="Data Tables (W)" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="70">
   <si>
     <t>FRN Franchise</t>
   </si>
@@ -68,9 +69,21 @@
     <t>2026 Q2</t>
   </si>
   <si>
+    <t>24Q2-25Q1</t>
+  </si>
+  <si>
+    <t>26Q1</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
     <t>Model Score</t>
   </si>
   <si>
+    <t>Franchise</t>
+  </si>
+  <si>
     <t>Gross Loss Impact</t>
   </si>
   <si>
@@ -98,18 +111,6 @@
     <t>FRN Independent</t>
   </si>
   <si>
-    <t>24Q2-25Q1</t>
-  </si>
-  <si>
-    <t>26Q1</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Franchise</t>
-  </si>
-  <si>
     <t>Independent</t>
   </si>
   <si>
@@ -125,13 +126,124 @@
     <t>frnf</t>
   </si>
   <si>
+    <t>added 60%</t>
+  </si>
+  <si>
     <t>frni</t>
   </si>
   <si>
-    <t>added 60%</t>
-  </si>
-  <si>
     <t>Cut 35%</t>
+  </si>
+  <si>
+    <t>2025-12-28/2026-01-03</t>
+  </si>
+  <si>
+    <t>2026-01-04/2026-01-10</t>
+  </si>
+  <si>
+    <t>2026-01-11/2026-01-17</t>
+  </si>
+  <si>
+    <t>2026-01-18/2026-01-24</t>
+  </si>
+  <si>
+    <t>2026-01-25/2026-01-31</t>
+  </si>
+  <si>
+    <t>2026-02-01/2026-02-07</t>
+  </si>
+  <si>
+    <t>2026-02-08/2026-02-14</t>
+  </si>
+  <si>
+    <t>2026-02-15/2026-02-21</t>
+  </si>
+  <si>
+    <t>2026-02-22/2026-02-28</t>
+  </si>
+  <si>
+    <t>2026-03-01/2026-03-07</t>
+  </si>
+  <si>
+    <t>2026-03-08/2026-03-14</t>
+  </si>
+  <si>
+    <t>2026-03-15/2026-03-21</t>
+  </si>
+  <si>
+    <t>2026-03-22/2026-03-28</t>
+  </si>
+  <si>
+    <t>2026-03-29/2026-04-04</t>
+  </si>
+  <si>
+    <t>2026-04-05/2026-04-11</t>
+  </si>
+  <si>
+    <t>2026-04-12/2026-04-18</t>
+  </si>
+  <si>
+    <t>2026-04-19/2026-04-25</t>
+  </si>
+  <si>
+    <t>2026-04-26/2026-05-02</t>
+  </si>
+  <si>
+    <t>2026-05-03/2026-05-09</t>
+  </si>
+  <si>
+    <t>2026-05-10/2026-05-16</t>
+  </si>
+  <si>
+    <t>2026-05-17/2026-05-23</t>
+  </si>
+  <si>
+    <t>2026-05-24/2026-05-30</t>
+  </si>
+  <si>
+    <t>2026-05-31/2026-06-06</t>
+  </si>
+  <si>
+    <t>2026-06-07/2026-06-13</t>
+  </si>
+  <si>
+    <t>2026-06-14/2026-06-20</t>
+  </si>
+  <si>
+    <t>2026-06-21/2026-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-28/2026-07-04</t>
+  </si>
+  <si>
+    <t>2026-07-05/2026-07-11</t>
+  </si>
+  <si>
+    <t>2026-07-12/2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-19/2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-26/2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-08-02/2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09/2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-08-16/2026-08-22</t>
+  </si>
+  <si>
+    <t>2026-08-23/2026-08-29</t>
+  </si>
+  <si>
+    <t>2026-08-30/2026-09-05</t>
+  </si>
+  <si>
+    <t>2026-09-06/2026-09-12</t>
   </si>
 </sst>
 </file>
@@ -186,15 +298,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,11 +619,12 @@
     <col min="6" max="7" width="12.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="11.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="12.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7265625" style="1"/>
+    <col min="12" max="12" width="8.7265625" style="1" customWidth="1"/>
     <col min="13" max="13" width="14.36328125" style="1" customWidth="1"/>
     <col min="14" max="14" width="18.453125" style="1" customWidth="1"/>
     <col min="15" max="17" width="15.453125" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.7265625" style="1"/>
+    <col min="18" max="18" width="8.7265625" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
@@ -548,18 +662,18 @@
         <v>10</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1">
         <v>138.1224155171237</v>
@@ -591,28 +705,28 @@
       <c r="K2" s="1">
         <v>142.51304336777719</v>
       </c>
-      <c r="M2" s="4" t="s">
-        <v>24</v>
+      <c r="M2" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O2" s="1">
-        <f>AVERAGE(C2:F2)</f>
+        <f t="shared" ref="O2:O10" si="0">AVERAGE(C2:F2)</f>
         <v>139.48515878674203</v>
       </c>
       <c r="P2" s="1">
-        <f>J2</f>
+        <f t="shared" ref="P2:P10" si="1">J2</f>
         <v>142.1274697075155</v>
       </c>
       <c r="Q2" s="1">
-        <f>P2-O2</f>
+        <f t="shared" ref="Q2:Q10" si="2">P2-O2</f>
         <v>2.6423109207734683</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1">
         <v>1.455103342337281</v>
@@ -644,26 +758,26 @@
       <c r="K3" s="1">
         <v>3.7388792212486521</v>
       </c>
-      <c r="M3" s="4"/>
+      <c r="M3" s="6"/>
       <c r="N3" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O3" s="1">
-        <f>AVERAGE(C3:F3)</f>
+        <f t="shared" si="0"/>
         <v>2.3498597848484977</v>
       </c>
       <c r="P3" s="1">
-        <f>J3</f>
+        <f t="shared" si="1"/>
         <v>3.476217260686326</v>
       </c>
       <c r="Q3" s="1">
-        <f t="shared" ref="Q3:Q10" si="0">P3-O3</f>
+        <f t="shared" si="2"/>
         <v>1.1263574758378283</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1">
         <v>-0.72863757468300028</v>
@@ -695,26 +809,26 @@
       <c r="K4" s="1">
         <v>3.3861820226881689</v>
       </c>
-      <c r="M4" s="4"/>
+      <c r="M4" s="6"/>
       <c r="N4" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O4" s="1">
-        <f>AVERAGE(C4:F4)</f>
+        <f t="shared" si="0"/>
         <v>1.5684387719037034</v>
       </c>
       <c r="P4" s="1">
-        <f>J4</f>
+        <f t="shared" si="1"/>
         <v>3.3293982523546042</v>
       </c>
       <c r="Q4" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.7609594804509008</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1">
         <v>5.6369974563683511</v>
@@ -746,26 +860,26 @@
       <c r="K5" s="1">
         <v>5.6732880807626076</v>
       </c>
-      <c r="M5" s="4"/>
+      <c r="M5" s="6"/>
       <c r="N5" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O5" s="1">
-        <f>AVERAGE(C5:F5)</f>
+        <f t="shared" si="0"/>
         <v>5.5495529543228193</v>
       </c>
       <c r="P5" s="1">
-        <f>J5</f>
+        <f t="shared" si="1"/>
         <v>5.5815303917852557</v>
       </c>
       <c r="Q5" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.197743746243642E-2</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B6" s="1">
         <v>0.1655751651815629</v>
@@ -797,26 +911,26 @@
       <c r="K6" s="1">
         <v>-0.22743498031990991</v>
       </c>
-      <c r="M6" s="4"/>
+      <c r="M6" s="6"/>
       <c r="N6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O6" s="1">
-        <f>AVERAGE(C6:F6)</f>
+        <f t="shared" si="0"/>
         <v>-0.1890685601089441</v>
       </c>
       <c r="P6" s="1">
-        <f>J6</f>
+        <f t="shared" si="1"/>
         <v>-0.23181351788158999</v>
       </c>
       <c r="Q6" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-4.2744957772645892E-2</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1">
         <v>144.6514539063279</v>
@@ -848,26 +962,26 @@
       <c r="K7" s="1">
         <v>155.08395771215669</v>
       </c>
-      <c r="M7" s="4"/>
+      <c r="M7" s="6"/>
       <c r="N7" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O7" s="1">
-        <f>AVERAGE(C7:F7)</f>
+        <f t="shared" si="0"/>
         <v>148.76394173770808</v>
       </c>
       <c r="P7" s="1">
-        <f>J7</f>
+        <f t="shared" si="1"/>
         <v>154.2828020944601</v>
       </c>
-      <c r="Q7" s="5">
-        <f t="shared" si="0"/>
+      <c r="Q7" s="4">
+        <f t="shared" si="2"/>
         <v>5.5188603567520147</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1">
         <v>71625171.829999998</v>
@@ -899,26 +1013,26 @@
       <c r="K8" s="1">
         <v>133176633.84999999</v>
       </c>
-      <c r="M8" s="4"/>
+      <c r="M8" s="6"/>
       <c r="N8" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O8" s="1">
-        <f>AVERAGE(C8:F8)</f>
+        <f t="shared" si="0"/>
         <v>73777048.554999992</v>
       </c>
       <c r="P8" s="2">
-        <f>J8</f>
+        <f t="shared" si="1"/>
         <v>116688893.65000001</v>
       </c>
       <c r="Q8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>42911845.095000014</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1">
         <v>1.4569069976514</v>
@@ -950,26 +1064,26 @@
       <c r="K9" s="1">
         <v>1.4545750877651591</v>
       </c>
-      <c r="M9" s="4"/>
+      <c r="M9" s="6"/>
       <c r="N9" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O9" s="1">
-        <f>AVERAGE(C9:F9)</f>
+        <f t="shared" si="0"/>
         <v>1.4625683132420821</v>
       </c>
       <c r="P9" s="1">
-        <f>J9</f>
+        <f t="shared" si="1"/>
         <v>1.4604856016312131</v>
       </c>
       <c r="Q9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2.0827116108690369E-3</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1">
         <v>0.24763464049740619</v>
@@ -1001,26 +1115,26 @@
       <c r="K10" s="1">
         <v>0.25324907114742728</v>
       </c>
-      <c r="M10" s="4"/>
+      <c r="M10" s="6"/>
       <c r="N10" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O10" s="1">
-        <f>AVERAGE(C10:F10)</f>
+        <f t="shared" si="0"/>
         <v>0.25270097943012776</v>
       </c>
       <c r="P10" s="1">
-        <f>J10</f>
+        <f t="shared" si="1"/>
         <v>0.25331162168402271</v>
       </c>
       <c r="Q10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>6.1064225389495519E-4</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>1</v>
@@ -1053,19 +1167,19 @@
         <v>10</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="P12" s="3" t="str">
-        <f>J12</f>
+        <f t="shared" ref="P12:P21" si="3">J12</f>
         <v>2026 Q1</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1">
         <v>138.02339833885611</v>
@@ -1097,28 +1211,28 @@
       <c r="K13" s="1">
         <v>145.04096387570121</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="M13" s="5" t="s">
         <v>25</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O13" s="1">
-        <f>AVERAGE(C13:F13)</f>
+        <f t="shared" ref="O13:O21" si="4">AVERAGE(C13:F13)</f>
         <v>141.36731743910732</v>
       </c>
       <c r="P13" s="1">
-        <f>J13</f>
+        <f t="shared" si="3"/>
         <v>144.61113226194979</v>
       </c>
       <c r="Q13" s="1">
-        <f>P13-O13</f>
+        <f t="shared" ref="Q13:Q21" si="5">P13-O13</f>
         <v>3.2438148228424666</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1">
         <v>-2.450434501423274</v>
@@ -1150,26 +1264,26 @@
       <c r="K14" s="1">
         <v>0.17601178619739241</v>
       </c>
-      <c r="M14" s="4"/>
+      <c r="M14" s="6"/>
       <c r="N14" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O14" s="1">
-        <f>AVERAGE(C14:F14)</f>
+        <f t="shared" si="4"/>
         <v>-1.7065223321159948</v>
       </c>
       <c r="P14" s="1">
-        <f>J14</f>
+        <f t="shared" si="3"/>
         <v>0.28903743444342922</v>
       </c>
       <c r="Q14" s="1">
-        <f t="shared" ref="Q14:Q21" si="1">P14-O14</f>
+        <f t="shared" si="5"/>
         <v>1.995559766559424</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1">
         <v>-2.265140967076638</v>
@@ -1201,26 +1315,26 @@
       <c r="K15" s="1">
         <v>0.53982364461653043</v>
       </c>
-      <c r="M15" s="4"/>
+      <c r="M15" s="6"/>
       <c r="N15" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O15" s="1">
-        <f>AVERAGE(C15:F15)</f>
+        <f t="shared" si="4"/>
         <v>-0.98787403636628734</v>
       </c>
       <c r="P15" s="1">
-        <f>J15</f>
+        <f t="shared" si="3"/>
         <v>0.8238534098899486</v>
       </c>
       <c r="Q15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>1.8117274462562358</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1">
         <v>4.6597308101274191</v>
@@ -1252,26 +1366,26 @@
       <c r="K16" s="1">
         <v>3.0059169907643071</v>
       </c>
-      <c r="M16" s="4"/>
+      <c r="M16" s="6"/>
       <c r="N16" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O16" s="1">
-        <f>AVERAGE(C16:F16)</f>
+        <f t="shared" si="4"/>
         <v>4.7163887721905322</v>
       </c>
       <c r="P16" s="1">
-        <f>J16</f>
+        <f t="shared" si="3"/>
         <v>3.6480792075265001</v>
       </c>
       <c r="Q16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-1.0683095646640322</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B17" s="1">
         <v>-6.1328506852409426E-3</v>
@@ -1303,26 +1417,26 @@
       <c r="K17" s="1">
         <v>-0.70072465953723073</v>
       </c>
-      <c r="M17" s="4"/>
+      <c r="M17" s="6"/>
       <c r="N17" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O17" s="1">
-        <f>AVERAGE(C17:F17)</f>
+        <f t="shared" si="4"/>
         <v>-0.36567445445260371</v>
       </c>
       <c r="P17" s="1">
-        <f>J17</f>
+        <f t="shared" si="3"/>
         <v>-0.83726061809499708</v>
       </c>
       <c r="Q17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>-0.47158616364239336</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B18" s="1">
         <v>137.96142082979841</v>
@@ -1354,26 +1468,26 @@
       <c r="K18" s="1">
         <v>148.06199163774221</v>
       </c>
-      <c r="M18" s="4"/>
+      <c r="M18" s="6"/>
       <c r="N18" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O18" s="1">
-        <f>AVERAGE(C18:F18)</f>
+        <f t="shared" si="4"/>
         <v>143.02363538836295</v>
       </c>
       <c r="P18" s="1">
-        <f>J18</f>
+        <f t="shared" si="3"/>
         <v>148.53484169571459</v>
       </c>
-      <c r="Q18" s="5">
-        <f t="shared" si="1"/>
+      <c r="Q18" s="4">
+        <f t="shared" si="5"/>
         <v>5.5112063073516424</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B19" s="1">
         <v>58980543.640000001</v>
@@ -1405,26 +1519,26 @@
       <c r="K19" s="1">
         <v>39082127.130000003</v>
       </c>
-      <c r="M19" s="4"/>
+      <c r="M19" s="6"/>
       <c r="N19" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O19" s="1">
-        <f>AVERAGE(C19:F19)</f>
+        <f t="shared" si="4"/>
         <v>62123073.965000004</v>
       </c>
       <c r="P19" s="2">
-        <f>J19</f>
+        <f t="shared" si="3"/>
         <v>41026540.079999998</v>
       </c>
       <c r="Q19" s="2">
-        <f>P19-O19</f>
+        <f t="shared" si="5"/>
         <v>-21096533.885000005</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B20" s="1">
         <v>1.5226412686800139</v>
@@ -1456,26 +1570,26 @@
       <c r="K20" s="1">
         <v>1.6485122884007339</v>
       </c>
-      <c r="M20" s="4"/>
+      <c r="M20" s="6"/>
       <c r="N20" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O20" s="1">
-        <f>AVERAGE(C20:F20)</f>
+        <f t="shared" si="4"/>
         <v>1.5186949805540475</v>
       </c>
       <c r="P20" s="1">
-        <f>J20</f>
+        <f t="shared" si="3"/>
         <v>1.5972430010815899</v>
       </c>
       <c r="Q20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>7.8548020527542395E-2</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B21" s="1">
         <v>0.2500876121526463</v>
@@ -1507,29 +1621,29 @@
       <c r="K21" s="1">
         <v>0.2600103522791033</v>
       </c>
-      <c r="M21" s="4"/>
+      <c r="M21" s="6"/>
       <c r="N21" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O21" s="1">
-        <f>AVERAGE(C21:F21)</f>
+        <f t="shared" si="4"/>
         <v>0.25522392077789435</v>
       </c>
       <c r="P21" s="1">
-        <f>J21</f>
+        <f t="shared" si="3"/>
         <v>0.26196086597278567</v>
       </c>
       <c r="Q21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>6.7369451948913195E-3</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="O22" s="5">
+      <c r="O22" s="4">
         <f>O18-O7</f>
         <v>-5.7403063493451327</v>
       </c>
-      <c r="P22" s="5">
+      <c r="P22" s="4">
         <f>P18-P7</f>
         <v>-5.747960398745505</v>
       </c>
@@ -1539,43 +1653,43 @@
         <v>26</v>
       </c>
       <c r="B23" s="1">
-        <f>B8/1000000</f>
+        <f t="shared" ref="B23:K23" si="6">B8/1000000</f>
         <v>71.625171829999999</v>
       </c>
       <c r="C23" s="1">
-        <f t="shared" ref="C23:K24" si="2">C8/1000000</f>
+        <f t="shared" si="6"/>
         <v>74.003857229999994</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>54.598117710000004</v>
       </c>
       <c r="E23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>62.62628814</v>
       </c>
       <c r="F23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>103.87993114</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>105.33041253</v>
       </c>
       <c r="H23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>99.848403939999997</v>
       </c>
       <c r="I23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>81.878054120000002</v>
       </c>
       <c r="J23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>116.68889365000001</v>
       </c>
       <c r="K23" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>133.17663385</v>
       </c>
     </row>
@@ -1584,43 +1698,43 @@
         <v>27</v>
       </c>
       <c r="B24" s="1">
-        <f>B19/1000000</f>
+        <f t="shared" ref="B24:K24" si="7">B19/1000000</f>
         <v>58.98054364</v>
       </c>
       <c r="C24" s="1">
-        <f t="shared" ref="C24:K24" si="3">C19/1000000</f>
+        <f t="shared" si="7"/>
         <v>70.438646550000001</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>52.61142727</v>
       </c>
       <c r="E24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>55.282841180000005</v>
       </c>
       <c r="F24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>70.159380859999999</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>72.608250330000004</v>
       </c>
       <c r="H24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>51.318850920000003</v>
       </c>
       <c r="I24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>34.24704801</v>
       </c>
       <c r="J24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>41.026540079999997</v>
       </c>
       <c r="K24" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>39.082127130000003</v>
       </c>
     </row>
@@ -1636,7 +1750,7 @@
         <v>0.58164220357784702</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
@@ -1650,7 +1764,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="O26" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P26" s="1">
         <f>P19/O19-1</f>
@@ -1678,4 +1792,2338 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:AL21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="20.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" t="s">
+        <v>49</v>
+      </c>
+      <c r="S1" t="s">
+        <v>50</v>
+      </c>
+      <c r="T1" t="s">
+        <v>51</v>
+      </c>
+      <c r="U1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V1" t="s">
+        <v>53</v>
+      </c>
+      <c r="W1" t="s">
+        <v>54</v>
+      </c>
+      <c r="X1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>141.49184031696501</v>
+      </c>
+      <c r="C2">
+        <v>141.94905606058981</v>
+      </c>
+      <c r="D2">
+        <v>142.50386369294301</v>
+      </c>
+      <c r="E2">
+        <v>142.55930543249389</v>
+      </c>
+      <c r="F2">
+        <v>141.3366953939975</v>
+      </c>
+      <c r="G2">
+        <v>141.9209281428254</v>
+      </c>
+      <c r="H2">
+        <v>142.45258142835411</v>
+      </c>
+      <c r="I2">
+        <v>142.17065495491471</v>
+      </c>
+      <c r="J2">
+        <v>142.24935142728239</v>
+      </c>
+      <c r="K2">
+        <v>142.08984296989999</v>
+      </c>
+      <c r="L2">
+        <v>142.07545860150421</v>
+      </c>
+      <c r="M2">
+        <v>142.15367414305601</v>
+      </c>
+      <c r="N2">
+        <v>142.61047116716429</v>
+      </c>
+      <c r="O2">
+        <v>142.38907084429161</v>
+      </c>
+      <c r="P2">
+        <v>143.13998871269169</v>
+      </c>
+      <c r="Q2">
+        <v>142.31748963992649</v>
+      </c>
+      <c r="R2">
+        <v>142.2243453924186</v>
+      </c>
+      <c r="S2">
+        <v>142.40601482654739</v>
+      </c>
+      <c r="T2">
+        <v>142.08203952561431</v>
+      </c>
+      <c r="U2">
+        <v>142.02714407751941</v>
+      </c>
+      <c r="V2">
+        <v>142.6130076157325</v>
+      </c>
+      <c r="W2">
+        <v>142.1735259486573</v>
+      </c>
+      <c r="X2">
+        <v>143.20919472833319</v>
+      </c>
+      <c r="Y2">
+        <v>143.50799809433599</v>
+      </c>
+      <c r="Z2">
+        <v>143.21370140357789</v>
+      </c>
+      <c r="AA2">
+        <v>142.6423991899396</v>
+      </c>
+      <c r="AB2">
+        <v>143.3499654045703</v>
+      </c>
+      <c r="AC2">
+        <v>143.3714955979236</v>
+      </c>
+      <c r="AD2">
+        <v>143.36354549876361</v>
+      </c>
+      <c r="AE2">
+        <v>143.6778156501189</v>
+      </c>
+      <c r="AF2">
+        <v>143.2786291808136</v>
+      </c>
+      <c r="AG2">
+        <v>142.5081410202549</v>
+      </c>
+      <c r="AH2">
+        <v>143.1821867347976</v>
+      </c>
+      <c r="AI2">
+        <v>142.80481120107629</v>
+      </c>
+      <c r="AJ2">
+        <v>143.70158435520619</v>
+      </c>
+      <c r="AK2">
+        <v>143.4869858015918</v>
+      </c>
+      <c r="AL2">
+        <v>142.7008409869735</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3">
+        <v>4.2535546599317797</v>
+      </c>
+      <c r="C3">
+        <v>3.7708201103708632</v>
+      </c>
+      <c r="D3">
+        <v>3.5671052931276681</v>
+      </c>
+      <c r="E3">
+        <v>3.8866032559355399</v>
+      </c>
+      <c r="F3">
+        <v>3.7356660172468712</v>
+      </c>
+      <c r="G3">
+        <v>3.3871230742051921</v>
+      </c>
+      <c r="H3">
+        <v>3.3354998728671599</v>
+      </c>
+      <c r="I3">
+        <v>3.2578725013498508</v>
+      </c>
+      <c r="J3">
+        <v>3.3798389381441321</v>
+      </c>
+      <c r="K3">
+        <v>3.332878688215033</v>
+      </c>
+      <c r="L3">
+        <v>3.4625230934663311</v>
+      </c>
+      <c r="M3">
+        <v>3.280274515093168</v>
+      </c>
+      <c r="N3">
+        <v>3.6997792777021061</v>
+      </c>
+      <c r="O3">
+        <v>3.631042125839115</v>
+      </c>
+      <c r="P3">
+        <v>3.5418133553601758</v>
+      </c>
+      <c r="Q3">
+        <v>4.2501001077609999</v>
+      </c>
+      <c r="R3">
+        <v>3.7322225852920212</v>
+      </c>
+      <c r="S3">
+        <v>3.9718441025441389</v>
+      </c>
+      <c r="T3">
+        <v>4.062570393359124</v>
+      </c>
+      <c r="U3">
+        <v>3.5612317667257689</v>
+      </c>
+      <c r="V3">
+        <v>3.7365377091432488</v>
+      </c>
+      <c r="W3">
+        <v>3.530087523848521</v>
+      </c>
+      <c r="X3">
+        <v>3.448893554052233</v>
+      </c>
+      <c r="Y3">
+        <v>3.8362550144545651</v>
+      </c>
+      <c r="Z3">
+        <v>3.7286689315892549</v>
+      </c>
+      <c r="AA3">
+        <v>3.797349677112237</v>
+      </c>
+      <c r="AB3">
+        <v>3.686541046191337</v>
+      </c>
+      <c r="AC3">
+        <v>3.759750470038369</v>
+      </c>
+      <c r="AD3">
+        <v>3.5463198356551691</v>
+      </c>
+      <c r="AE3">
+        <v>3.7238367479087908</v>
+      </c>
+      <c r="AF3">
+        <v>3.3984335514542749</v>
+      </c>
+      <c r="AG3">
+        <v>3.5677925197126679</v>
+      </c>
+      <c r="AH3">
+        <v>3.4900720422649272</v>
+      </c>
+      <c r="AI3">
+        <v>3.609624176110628</v>
+      </c>
+      <c r="AJ3">
+        <v>2.933700026426123</v>
+      </c>
+      <c r="AK3">
+        <v>4.4405610121497432</v>
+      </c>
+      <c r="AL3">
+        <v>4.6200395943550916</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>5.1211366777608722</v>
+      </c>
+      <c r="C4">
+        <v>5.3413862177032527</v>
+      </c>
+      <c r="D4">
+        <v>3.236406065765411</v>
+      </c>
+      <c r="E4">
+        <v>3.6759564656770389</v>
+      </c>
+      <c r="F4">
+        <v>3.8829326795430879</v>
+      </c>
+      <c r="G4">
+        <v>3.0595781605286838</v>
+      </c>
+      <c r="H4">
+        <v>3.1573789161319539</v>
+      </c>
+      <c r="I4">
+        <v>3.6364909513198471</v>
+      </c>
+      <c r="J4">
+        <v>3.023744373517403</v>
+      </c>
+      <c r="K4">
+        <v>2.3592559268387769</v>
+      </c>
+      <c r="L4">
+        <v>2.741372517873911</v>
+      </c>
+      <c r="M4">
+        <v>3.2607923559607901</v>
+      </c>
+      <c r="N4">
+        <v>2.9143224098528022</v>
+      </c>
+      <c r="O4">
+        <v>3.8642964959448838</v>
+      </c>
+      <c r="P4">
+        <v>2.8911753276527041</v>
+      </c>
+      <c r="Q4">
+        <v>3.883821777179326</v>
+      </c>
+      <c r="R4">
+        <v>3.3683747970188058</v>
+      </c>
+      <c r="S4">
+        <v>3.5258566133433109</v>
+      </c>
+      <c r="T4">
+        <v>4.8056309318470261</v>
+      </c>
+      <c r="U4">
+        <v>4.5483505390990944</v>
+      </c>
+      <c r="V4">
+        <v>3.8305471628224952</v>
+      </c>
+      <c r="W4">
+        <v>3.7445447937660359</v>
+      </c>
+      <c r="X4">
+        <v>2.9764914782512282</v>
+      </c>
+      <c r="Y4">
+        <v>3.0322682696834069</v>
+      </c>
+      <c r="Z4">
+        <v>3.276113801459124</v>
+      </c>
+      <c r="AA4">
+        <v>2.8051778400015102</v>
+      </c>
+      <c r="AB4">
+        <v>2.9558203162353469</v>
+      </c>
+      <c r="AC4">
+        <v>3.007083461059286</v>
+      </c>
+      <c r="AD4">
+        <v>3.5140815245267429</v>
+      </c>
+      <c r="AE4">
+        <v>2.977484859465338</v>
+      </c>
+      <c r="AF4">
+        <v>3.1373194318373341</v>
+      </c>
+      <c r="AG4">
+        <v>4.2974471145368316</v>
+      </c>
+      <c r="AH4">
+        <v>3.0971190078941802</v>
+      </c>
+      <c r="AI4">
+        <v>3.2080264977108941</v>
+      </c>
+      <c r="AJ4">
+        <v>3.4539606971427101</v>
+      </c>
+      <c r="AK4">
+        <v>3.9806766612698499</v>
+      </c>
+      <c r="AL4">
+        <v>5.3239250506192617</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5">
+        <v>5.8680947013860907</v>
+      </c>
+      <c r="C5">
+        <v>6.1416821269859794</v>
+      </c>
+      <c r="D5">
+        <v>5.6906776547890026</v>
+      </c>
+      <c r="E5">
+        <v>5.6929335422887766</v>
+      </c>
+      <c r="F5">
+        <v>5.0818439302076364</v>
+      </c>
+      <c r="G5">
+        <v>5.4660944540901708</v>
+      </c>
+      <c r="H5">
+        <v>5.3525303705038239</v>
+      </c>
+      <c r="I5">
+        <v>5.6596660101450134</v>
+      </c>
+      <c r="J5">
+        <v>5.5892847161095567</v>
+      </c>
+      <c r="K5">
+        <v>5.7298625378186241</v>
+      </c>
+      <c r="L5">
+        <v>5.7965736861109951</v>
+      </c>
+      <c r="M5">
+        <v>5.4418977503412114</v>
+      </c>
+      <c r="N5">
+        <v>5.506211867105745</v>
+      </c>
+      <c r="O5">
+        <v>5.6195668599695372</v>
+      </c>
+      <c r="P5">
+        <v>5.6084378760632108</v>
+      </c>
+      <c r="Q5">
+        <v>5.417563833762415</v>
+      </c>
+      <c r="R5">
+        <v>5.9955919708351306</v>
+      </c>
+      <c r="S5">
+        <v>6.0269167394767562</v>
+      </c>
+      <c r="T5">
+        <v>6.0318939840662704</v>
+      </c>
+      <c r="U5">
+        <v>6.2874423474943626</v>
+      </c>
+      <c r="V5">
+        <v>5.377118045973134</v>
+      </c>
+      <c r="W5">
+        <v>5.6103133594167458</v>
+      </c>
+      <c r="X5">
+        <v>5.6271884043249649</v>
+      </c>
+      <c r="Y5">
+        <v>4.9557198028191287</v>
+      </c>
+      <c r="Z5">
+        <v>5.6594902937064999</v>
+      </c>
+      <c r="AA5">
+        <v>5.3577533423193149</v>
+      </c>
+      <c r="AB5">
+        <v>5.2952397187486291</v>
+      </c>
+      <c r="AC5">
+        <v>5.0230944058329072</v>
+      </c>
+      <c r="AD5">
+        <v>5.0628359932324374</v>
+      </c>
+      <c r="AE5">
+        <v>5.5875962731156994</v>
+      </c>
+      <c r="AF5">
+        <v>5.1953516336274728</v>
+      </c>
+      <c r="AG5">
+        <v>5.1467090313886708</v>
+      </c>
+      <c r="AH5">
+        <v>4.7444389253418464</v>
+      </c>
+      <c r="AI5">
+        <v>5.647843485397396</v>
+      </c>
+      <c r="AJ5">
+        <v>5.3991803824350733</v>
+      </c>
+      <c r="AK5">
+        <v>5.6553133858171716</v>
+      </c>
+      <c r="AL5">
+        <v>5.5004309061243237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
+        <v>-1.3450249066497831E-2</v>
+      </c>
+      <c r="C6">
+        <v>-0.30466222991159808</v>
+      </c>
+      <c r="D6">
+        <v>-0.36769023765249043</v>
+      </c>
+      <c r="E6">
+        <v>-1.431727779025615E-2</v>
+      </c>
+      <c r="F6">
+        <v>-0.32923515064299691</v>
+      </c>
+      <c r="G6">
+        <v>-0.42347210168746929</v>
+      </c>
+      <c r="H6">
+        <v>-0.30847986304890879</v>
+      </c>
+      <c r="I6">
+        <v>-3.6608842947873921E-2</v>
+      </c>
+      <c r="J6">
+        <v>-0.17896822871812379</v>
+      </c>
+      <c r="K6">
+        <v>-0.33713158627740158</v>
+      </c>
+      <c r="L6">
+        <v>-0.15172107033700921</v>
+      </c>
+      <c r="M6">
+        <v>-0.1862742775500226</v>
+      </c>
+      <c r="N6">
+        <v>-0.33482015015753652</v>
+      </c>
+      <c r="O6">
+        <v>1.5995271242535969E-2</v>
+      </c>
+      <c r="P6">
+        <v>-0.1768689700962989</v>
+      </c>
+      <c r="Q6">
+        <v>-9.8746361340175115E-2</v>
+      </c>
+      <c r="R6">
+        <v>-0.2246309877598035</v>
+      </c>
+      <c r="S6">
+        <v>-1.311005914675312E-2</v>
+      </c>
+      <c r="T6">
+        <v>-0.27208728769303298</v>
+      </c>
+      <c r="U6">
+        <v>-4.3125090521731753E-2</v>
+      </c>
+      <c r="V6">
+        <v>-9.8557761540407629E-2</v>
+      </c>
+      <c r="W6">
+        <v>-0.4907724994528373</v>
+      </c>
+      <c r="X6">
+        <v>-0.46198355396557361</v>
+      </c>
+      <c r="Y6">
+        <v>-0.1806793679564378</v>
+      </c>
+      <c r="Z6">
+        <v>-0.37447628528581411</v>
+      </c>
+      <c r="AA6">
+        <v>-0.48167707120475522</v>
+      </c>
+      <c r="AB6">
+        <v>-0.43691665984651801</v>
+      </c>
+      <c r="AC6">
+        <v>-0.1715514946619329</v>
+      </c>
+      <c r="AD6">
+        <v>-0.4330530176647468</v>
+      </c>
+      <c r="AE6">
+        <v>-0.173262489790284</v>
+      </c>
+      <c r="AF6">
+        <v>-0.47157137896447199</v>
+      </c>
+      <c r="AG6">
+        <v>-0.56059747003284532</v>
+      </c>
+      <c r="AH6">
+        <v>-0.44953353402994328</v>
+      </c>
+      <c r="AI6">
+        <v>-0.30087190263501318</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.44020142903119391</v>
+      </c>
+      <c r="AK6">
+        <v>-2.7995018118636691E-2</v>
+      </c>
+      <c r="AL6">
+        <v>-0.70971485637616072</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7">
+        <v>156.72117610697731</v>
+      </c>
+      <c r="C7">
+        <v>156.89828228573819</v>
+      </c>
+      <c r="D7">
+        <v>154.63036246897261</v>
+      </c>
+      <c r="E7">
+        <v>155.80048141860499</v>
+      </c>
+      <c r="F7">
+        <v>153.70790287035209</v>
+      </c>
+      <c r="G7">
+        <v>153.41025172996191</v>
+      </c>
+      <c r="H7">
+        <v>153.9895107248081</v>
+      </c>
+      <c r="I7">
+        <v>154.68807557478149</v>
+      </c>
+      <c r="J7">
+        <v>154.0632512263353</v>
+      </c>
+      <c r="K7">
+        <v>153.1747085364951</v>
+      </c>
+      <c r="L7">
+        <v>153.92420682861851</v>
+      </c>
+      <c r="M7">
+        <v>153.95036448690121</v>
+      </c>
+      <c r="N7">
+        <v>154.39596457166741</v>
+      </c>
+      <c r="O7">
+        <v>155.51997159728771</v>
+      </c>
+      <c r="P7">
+        <v>155.0045463016715</v>
+      </c>
+      <c r="Q7">
+        <v>155.770228997289</v>
+      </c>
+      <c r="R7">
+        <v>155.09590375780479</v>
+      </c>
+      <c r="S7">
+        <v>155.9175222227648</v>
+      </c>
+      <c r="T7">
+        <v>156.71004754719371</v>
+      </c>
+      <c r="U7">
+        <v>156.3810436403169</v>
+      </c>
+      <c r="V7">
+        <v>155.45865277213099</v>
+      </c>
+      <c r="W7">
+        <v>154.56769912623579</v>
+      </c>
+      <c r="X7">
+        <v>154.79978461099611</v>
+      </c>
+      <c r="Y7">
+        <v>155.15156181333671</v>
+      </c>
+      <c r="Z7">
+        <v>155.50349814504699</v>
+      </c>
+      <c r="AA7">
+        <v>154.12100297816789</v>
+      </c>
+      <c r="AB7">
+        <v>154.85064982589901</v>
+      </c>
+      <c r="AC7">
+        <v>154.98987244019219</v>
+      </c>
+      <c r="AD7">
+        <v>155.05372983451321</v>
+      </c>
+      <c r="AE7">
+        <v>155.79347104081839</v>
+      </c>
+      <c r="AF7">
+        <v>154.53816241876811</v>
+      </c>
+      <c r="AG7">
+        <v>154.95949221586019</v>
+      </c>
+      <c r="AH7">
+        <v>154.06428317626859</v>
+      </c>
+      <c r="AI7">
+        <v>154.96943345766019</v>
+      </c>
+      <c r="AJ7">
+        <v>155.04822403217889</v>
+      </c>
+      <c r="AK7">
+        <v>157.5355418427099</v>
+      </c>
+      <c r="AL7">
+        <v>157.435521681696</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8">
+        <v>5215570.8800000008</v>
+      </c>
+      <c r="C8">
+        <v>6720458.8799999999</v>
+      </c>
+      <c r="D8">
+        <v>5597428.0499999989</v>
+      </c>
+      <c r="E8">
+        <v>6350677.7400000002</v>
+      </c>
+      <c r="F8">
+        <v>6723450.96</v>
+      </c>
+      <c r="G8">
+        <v>7816332.790000001</v>
+      </c>
+      <c r="H8">
+        <v>8196388.7799999993</v>
+      </c>
+      <c r="I8">
+        <v>11084000.65</v>
+      </c>
+      <c r="J8">
+        <v>18597895.809999999</v>
+      </c>
+      <c r="K8">
+        <v>13912984.82</v>
+      </c>
+      <c r="L8">
+        <v>12890139.01</v>
+      </c>
+      <c r="M8">
+        <v>10547556.99</v>
+      </c>
+      <c r="N8">
+        <v>10958778.74</v>
+      </c>
+      <c r="O8">
+        <v>12727106.52</v>
+      </c>
+      <c r="P8">
+        <v>10356902.75</v>
+      </c>
+      <c r="Q8">
+        <v>10572336.890000001</v>
+      </c>
+      <c r="R8">
+        <v>11156184.189999999</v>
+      </c>
+      <c r="S8">
+        <v>11367264.119999999</v>
+      </c>
+      <c r="T8">
+        <v>11754983.369999999</v>
+      </c>
+      <c r="U8">
+        <v>9879963.4000000004</v>
+      </c>
+      <c r="V8">
+        <v>9356436.7600000016</v>
+      </c>
+      <c r="W8">
+        <v>10375380.98</v>
+      </c>
+      <c r="X8">
+        <v>8759954.2999999989</v>
+      </c>
+      <c r="Y8">
+        <v>7915672.75</v>
+      </c>
+      <c r="Z8">
+        <v>9006047.6099999994</v>
+      </c>
+      <c r="AA8">
+        <v>8170396.3499999996</v>
+      </c>
+      <c r="AB8">
+        <v>8523155.5300000012</v>
+      </c>
+      <c r="AC8">
+        <v>8536968.2699999996</v>
+      </c>
+      <c r="AD8">
+        <v>7320010.4500000002</v>
+      </c>
+      <c r="AE8">
+        <v>7897686.4500000002</v>
+      </c>
+      <c r="AF8">
+        <v>8304710.7000000002</v>
+      </c>
+      <c r="AG8">
+        <v>8759862.3399999999</v>
+      </c>
+      <c r="AH8">
+        <v>7121767.8100000015</v>
+      </c>
+      <c r="AI8">
+        <v>7600854.71</v>
+      </c>
+      <c r="AJ8">
+        <v>7571621.9800000004</v>
+      </c>
+      <c r="AK8">
+        <v>5544028.0500000007</v>
+      </c>
+      <c r="AL8">
+        <v>2498114.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9">
+        <v>1.44218398737001</v>
+      </c>
+      <c r="C9">
+        <v>1.4251340857171899</v>
+      </c>
+      <c r="D9">
+        <v>1.4534603374015751</v>
+      </c>
+      <c r="E9">
+        <v>1.4533158499997829</v>
+      </c>
+      <c r="F9">
+        <v>1.4935346932184339</v>
+      </c>
+      <c r="G9">
+        <v>1.4679899110811261</v>
+      </c>
+      <c r="H9">
+        <v>1.4754481686565599</v>
+      </c>
+      <c r="I9">
+        <v>1.455449519213321</v>
+      </c>
+      <c r="J9">
+        <v>1.4599842542371559</v>
+      </c>
+      <c r="K9">
+        <v>1.450954661301928</v>
+      </c>
+      <c r="L9">
+        <v>1.4467086349951499</v>
+      </c>
+      <c r="M9">
+        <v>1.4695726879647939</v>
+      </c>
+      <c r="N9">
+        <v>1.465373213170643</v>
+      </c>
+      <c r="O9">
+        <v>1.4580296874899761</v>
+      </c>
+      <c r="P9">
+        <v>1.458747401337168</v>
+      </c>
+      <c r="Q9">
+        <v>1.471167886241493</v>
+      </c>
+      <c r="R9">
+        <v>1.434187910527718</v>
+      </c>
+      <c r="S9">
+        <v>1.432236906622411</v>
+      </c>
+      <c r="T9">
+        <v>1.4319273969746451</v>
+      </c>
+      <c r="U9">
+        <v>1.416213919410884</v>
+      </c>
+      <c r="V9">
+        <v>1.4738269661108081</v>
+      </c>
+      <c r="W9">
+        <v>1.4586264009589449</v>
+      </c>
+      <c r="X9">
+        <v>1.457538577514836</v>
+      </c>
+      <c r="Y9">
+        <v>1.502114268909797</v>
+      </c>
+      <c r="Z9">
+        <v>1.4554608057163561</v>
+      </c>
+      <c r="AA9">
+        <v>1.4751034907239371</v>
+      </c>
+      <c r="AB9">
+        <v>1.4792395334626649</v>
+      </c>
+      <c r="AC9">
+        <v>1.4975188950407039</v>
+      </c>
+      <c r="AD9">
+        <v>1.4948214277673231</v>
+      </c>
+      <c r="AE9">
+        <v>1.4600933893640371</v>
+      </c>
+      <c r="AF9">
+        <v>1.485896711365142</v>
+      </c>
+      <c r="AG9">
+        <v>1.4891603060868881</v>
+      </c>
+      <c r="AH9">
+        <v>1.5167096338164781</v>
+      </c>
+      <c r="AI9">
+        <v>1.456209286383688</v>
+      </c>
+      <c r="AJ9">
+        <v>1.472375302886626</v>
+      </c>
+      <c r="AK9">
+        <v>1.45572914566904</v>
+      </c>
+      <c r="AL9">
+        <v>1.4657497066433189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10">
+        <v>0.25019214641523568</v>
+      </c>
+      <c r="C10">
+        <v>0.25435231757016569</v>
+      </c>
+      <c r="D10">
+        <v>0.25525271768074992</v>
+      </c>
+      <c r="E10">
+        <v>0.2502045325398608</v>
+      </c>
+      <c r="F10">
+        <v>0.25470335929490001</v>
+      </c>
+      <c r="G10">
+        <v>0.25604960145267808</v>
+      </c>
+      <c r="H10">
+        <v>0.25440685518641298</v>
+      </c>
+      <c r="I10">
+        <v>0.25052298347068391</v>
+      </c>
+      <c r="J10">
+        <v>0.25255668898168748</v>
+      </c>
+      <c r="K10">
+        <v>0.25481616551824859</v>
+      </c>
+      <c r="L10">
+        <v>0.25216744386195727</v>
+      </c>
+      <c r="M10">
+        <v>0.25266106110785752</v>
+      </c>
+      <c r="N10">
+        <v>0.25478314500225052</v>
+      </c>
+      <c r="O10">
+        <v>0.2497714961251066</v>
+      </c>
+      <c r="P10">
+        <v>0.25252669957280433</v>
+      </c>
+      <c r="Q10">
+        <v>0.25141066230485959</v>
+      </c>
+      <c r="R10">
+        <v>0.25320901411085428</v>
+      </c>
+      <c r="S10">
+        <v>0.25018728655923927</v>
+      </c>
+      <c r="T10">
+        <v>0.25388696125275761</v>
+      </c>
+      <c r="U10">
+        <v>0.25061607272173902</v>
+      </c>
+      <c r="V10">
+        <v>0.25140796802200582</v>
+      </c>
+      <c r="W10">
+        <v>0.2570110357064691</v>
+      </c>
+      <c r="X10">
+        <v>0.25659976505665111</v>
+      </c>
+      <c r="Y10">
+        <v>0.25258113382794911</v>
+      </c>
+      <c r="Z10">
+        <v>0.25534966121836877</v>
+      </c>
+      <c r="AA10">
+        <v>0.25688110101721079</v>
+      </c>
+      <c r="AB10">
+        <v>0.25624166656923603</v>
+      </c>
+      <c r="AC10">
+        <v>0.25245073563802761</v>
+      </c>
+      <c r="AD10">
+        <v>0.25618647168092501</v>
+      </c>
+      <c r="AE10">
+        <v>0.25247517842557549</v>
+      </c>
+      <c r="AF10">
+        <v>0.25673673398520669</v>
+      </c>
+      <c r="AG10">
+        <v>0.2580085352861835</v>
+      </c>
+      <c r="AH10">
+        <v>0.25642190762899919</v>
+      </c>
+      <c r="AI10">
+        <v>0.25429817003764299</v>
+      </c>
+      <c r="AJ10">
+        <v>0.25628859184330283</v>
+      </c>
+      <c r="AK10">
+        <v>0.25039992883026618</v>
+      </c>
+      <c r="AL10">
+        <v>0.26013878366251658</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" t="s">
+        <v>42</v>
+      </c>
+      <c r="L12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" t="s">
+        <v>44</v>
+      </c>
+      <c r="N12" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" t="s">
+        <v>46</v>
+      </c>
+      <c r="P12" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>48</v>
+      </c>
+      <c r="R12" t="s">
+        <v>49</v>
+      </c>
+      <c r="S12" t="s">
+        <v>50</v>
+      </c>
+      <c r="T12" t="s">
+        <v>51</v>
+      </c>
+      <c r="U12" t="s">
+        <v>52</v>
+      </c>
+      <c r="V12" t="s">
+        <v>53</v>
+      </c>
+      <c r="W12" t="s">
+        <v>54</v>
+      </c>
+      <c r="X12" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>64</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>68</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>145.58762014801491</v>
+      </c>
+      <c r="C13">
+        <v>145.27758700107989</v>
+      </c>
+      <c r="D13">
+        <v>144.6428236331794</v>
+      </c>
+      <c r="E13">
+        <v>144.83095792072339</v>
+      </c>
+      <c r="F13">
+        <v>144.20855603165001</v>
+      </c>
+      <c r="G13">
+        <v>144.31895850923621</v>
+      </c>
+      <c r="H13">
+        <v>144.79870482908609</v>
+      </c>
+      <c r="I13">
+        <v>144.59766330320099</v>
+      </c>
+      <c r="J13">
+        <v>144.58989587291529</v>
+      </c>
+      <c r="K13">
+        <v>143.88847010683281</v>
+      </c>
+      <c r="L13">
+        <v>144.59801921845539</v>
+      </c>
+      <c r="M13">
+        <v>144.53590247047271</v>
+      </c>
+      <c r="N13">
+        <v>144.81500345917769</v>
+      </c>
+      <c r="O13">
+        <v>145.0388969809502</v>
+      </c>
+      <c r="P13">
+        <v>144.94114171298469</v>
+      </c>
+      <c r="Q13">
+        <v>144.76623270729451</v>
+      </c>
+      <c r="R13">
+        <v>145.36806937154461</v>
+      </c>
+      <c r="S13">
+        <v>144.6869004601545</v>
+      </c>
+      <c r="T13">
+        <v>145.3034280373829</v>
+      </c>
+      <c r="U13">
+        <v>145.45132404403199</v>
+      </c>
+      <c r="V13">
+        <v>144.16617089724099</v>
+      </c>
+      <c r="W13">
+        <v>145.36040826620729</v>
+      </c>
+      <c r="X13">
+        <v>145.66192918141371</v>
+      </c>
+      <c r="Y13">
+        <v>145.8417068440385</v>
+      </c>
+      <c r="Z13">
+        <v>145.1592777667895</v>
+      </c>
+      <c r="AA13">
+        <v>144.61618764674131</v>
+      </c>
+      <c r="AB13">
+        <v>146.08146877649011</v>
+      </c>
+      <c r="AC13">
+        <v>146.15267127100259</v>
+      </c>
+      <c r="AD13">
+        <v>146.21141207044971</v>
+      </c>
+      <c r="AE13">
+        <v>145.35384796222471</v>
+      </c>
+      <c r="AF13">
+        <v>145.72531295232369</v>
+      </c>
+      <c r="AG13">
+        <v>147.42876888596129</v>
+      </c>
+      <c r="AH13">
+        <v>146.27994271613969</v>
+      </c>
+      <c r="AI13">
+        <v>146.25297457545881</v>
+      </c>
+      <c r="AJ13">
+        <v>145.4172927920217</v>
+      </c>
+      <c r="AK13">
+        <v>148.14814180133999</v>
+      </c>
+      <c r="AL13">
+        <v>144.69414119023369</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>-0.74255075862055264</v>
+      </c>
+      <c r="C14">
+        <v>8.4437070972768424E-2</v>
+      </c>
+      <c r="D14">
+        <v>0.54141735266387059</v>
+      </c>
+      <c r="E14">
+        <v>0.90665174918891012</v>
+      </c>
+      <c r="F14">
+        <v>0.28074144082515318</v>
+      </c>
+      <c r="G14">
+        <v>0.2317005453929539</v>
+      </c>
+      <c r="H14">
+        <v>1.117844495016612</v>
+      </c>
+      <c r="I14">
+        <v>0.41578126829796253</v>
+      </c>
+      <c r="J14">
+        <v>-6.1985355376606321E-2</v>
+      </c>
+      <c r="K14">
+        <v>0.3752244529903237</v>
+      </c>
+      <c r="L14">
+        <v>0.36799732516655581</v>
+      </c>
+      <c r="M14">
+        <v>-5.8928561486482067E-4</v>
+      </c>
+      <c r="N14">
+        <v>0.57779734437508523</v>
+      </c>
+      <c r="O14">
+        <v>-0.29367625394758079</v>
+      </c>
+      <c r="P14">
+        <v>-2.950948178488488E-2</v>
+      </c>
+      <c r="Q14">
+        <v>0.53252147203613731</v>
+      </c>
+      <c r="R14">
+        <v>0.30656610513915439</v>
+      </c>
+      <c r="S14">
+        <v>0.12004337428885491</v>
+      </c>
+      <c r="T14">
+        <v>8.3277153438729101E-2</v>
+      </c>
+      <c r="U14">
+        <v>0.1440085743047064</v>
+      </c>
+      <c r="V14">
+        <v>0.47523943505748889</v>
+      </c>
+      <c r="W14">
+        <v>0.47181597350578391</v>
+      </c>
+      <c r="X14">
+        <v>-3.9654478283154049E-2</v>
+      </c>
+      <c r="Y14">
+        <v>-0.76109100808477592</v>
+      </c>
+      <c r="Z14">
+        <v>0.78691343761587973</v>
+      </c>
+      <c r="AA14">
+        <v>0.72968173185080332</v>
+      </c>
+      <c r="AB14">
+        <v>0.2163711397267036</v>
+      </c>
+      <c r="AC14">
+        <v>0.87664767028897472</v>
+      </c>
+      <c r="AD14">
+        <v>-0.1026387326279234</v>
+      </c>
+      <c r="AE14">
+        <v>0.68087470386771543</v>
+      </c>
+      <c r="AF14">
+        <v>0.48880205102886981</v>
+      </c>
+      <c r="AG14">
+        <v>0.81636935218796225</v>
+      </c>
+      <c r="AH14">
+        <v>0.42226919694965659</v>
+      </c>
+      <c r="AI14">
+        <v>-1.085725520107758</v>
+      </c>
+      <c r="AJ14">
+        <v>2.1920435858766041</v>
+      </c>
+      <c r="AK14">
+        <v>3.2388663639803781</v>
+      </c>
+      <c r="AL14">
+        <v>3.444642625667655</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>2.1823601689405221</v>
+      </c>
+      <c r="C15">
+        <v>1.8450681698200451</v>
+      </c>
+      <c r="D15">
+        <v>0.69240351240062592</v>
+      </c>
+      <c r="E15">
+        <v>0.81890844917151784</v>
+      </c>
+      <c r="F15">
+        <v>1.2367136034179309</v>
+      </c>
+      <c r="G15">
+        <v>2.264113250823613</v>
+      </c>
+      <c r="H15">
+        <v>0.83158731472517555</v>
+      </c>
+      <c r="I15">
+        <v>0.67739121710617989</v>
+      </c>
+      <c r="J15">
+        <v>-0.32761385004872379</v>
+      </c>
+      <c r="K15">
+        <v>-0.34143144218589833</v>
+      </c>
+      <c r="L15">
+        <v>0.79908291645412777</v>
+      </c>
+      <c r="M15">
+        <v>0.79574714966180771</v>
+      </c>
+      <c r="N15">
+        <v>1.5947974732376939</v>
+      </c>
+      <c r="O15">
+        <v>-7.3748833469796923E-2</v>
+      </c>
+      <c r="P15">
+        <v>-4.2152588876455857E-2</v>
+      </c>
+      <c r="Q15">
+        <v>0.36408308208776508</v>
+      </c>
+      <c r="R15">
+        <v>0.4369026783958897</v>
+      </c>
+      <c r="S15">
+        <v>0.2810322861300813</v>
+      </c>
+      <c r="T15">
+        <v>0.11908919408131061</v>
+      </c>
+      <c r="U15">
+        <v>0.45112834029200571</v>
+      </c>
+      <c r="V15">
+        <v>0.80807423887193974</v>
+      </c>
+      <c r="W15">
+        <v>1.046195084449284</v>
+      </c>
+      <c r="X15">
+        <v>1.705483727886423</v>
+      </c>
+      <c r="Y15">
+        <v>0.34766488649945848</v>
+      </c>
+      <c r="Z15">
+        <v>1.3428043697410139</v>
+      </c>
+      <c r="AA15">
+        <v>0.14221974459654649</v>
+      </c>
+      <c r="AB15">
+        <v>-0.90568040042123499</v>
+      </c>
+      <c r="AC15">
+        <v>0.27038107336247957</v>
+      </c>
+      <c r="AD15">
+        <v>0.59319689879295401</v>
+      </c>
+      <c r="AE15">
+        <v>-0.55790746721652462</v>
+      </c>
+      <c r="AF15">
+        <v>0.27078438315128228</v>
+      </c>
+      <c r="AG15">
+        <v>0.82356132525582781</v>
+      </c>
+      <c r="AH15">
+        <v>-4.8680978827552228E-2</v>
+      </c>
+      <c r="AI15">
+        <v>2.097780496320699</v>
+      </c>
+      <c r="AJ15">
+        <v>1.858294326624631</v>
+      </c>
+      <c r="AK15">
+        <v>0.59893238193451204</v>
+      </c>
+      <c r="AL15">
+        <v>1.0250246699271759</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>5.9669044425939433</v>
+      </c>
+      <c r="C16">
+        <v>6.2126716305742029</v>
+      </c>
+      <c r="D16">
+        <v>4.1043513692549087</v>
+      </c>
+      <c r="E16">
+        <v>3.372064634951216</v>
+      </c>
+      <c r="F16">
+        <v>3.6332777867694999</v>
+      </c>
+      <c r="G16">
+        <v>3.5438491930565141</v>
+      </c>
+      <c r="H16">
+        <v>2.7950173834687191</v>
+      </c>
+      <c r="I16">
+        <v>2.5850445732592831</v>
+      </c>
+      <c r="J16">
+        <v>3.309528162113903</v>
+      </c>
+      <c r="K16">
+        <v>3.3664011513158512</v>
+      </c>
+      <c r="L16">
+        <v>3.627182443742218</v>
+      </c>
+      <c r="M16">
+        <v>3.329771236388642</v>
+      </c>
+      <c r="N16">
+        <v>3.4692559628418072</v>
+      </c>
+      <c r="O16">
+        <v>2.745344255066958</v>
+      </c>
+      <c r="P16">
+        <v>3.7108557755366629</v>
+      </c>
+      <c r="Q16">
+        <v>3.7120346562522761</v>
+      </c>
+      <c r="R16">
+        <v>2.6817243924430878</v>
+      </c>
+      <c r="S16">
+        <v>3.0716783118614752</v>
+      </c>
+      <c r="T16">
+        <v>1.9997471677310541</v>
+      </c>
+      <c r="U16">
+        <v>2.216372293981856</v>
+      </c>
+      <c r="V16">
+        <v>2.5119780510459111</v>
+      </c>
+      <c r="W16">
+        <v>3.5752149169820382</v>
+      </c>
+      <c r="X16">
+        <v>2.9832281465959838</v>
+      </c>
+      <c r="Y16">
+        <v>3.8527225569907388</v>
+      </c>
+      <c r="Z16">
+        <v>2.7739095987112621</v>
+      </c>
+      <c r="AA16">
+        <v>3.243666545022363</v>
+      </c>
+      <c r="AB16">
+        <v>3.5831129244023359</v>
+      </c>
+      <c r="AC16">
+        <v>2.820040190709439</v>
+      </c>
+      <c r="AD16">
+        <v>2.329569704110543</v>
+      </c>
+      <c r="AE16">
+        <v>1.76218941526605</v>
+      </c>
+      <c r="AF16">
+        <v>2.1135098621785331</v>
+      </c>
+      <c r="AG16">
+        <v>4.2886052956250724</v>
+      </c>
+      <c r="AH16">
+        <v>4.159751326445722</v>
+      </c>
+      <c r="AI16">
+        <v>2.6309264583068761</v>
+      </c>
+      <c r="AJ16">
+        <v>2.2030118279944459</v>
+      </c>
+      <c r="AK16">
+        <v>2.5950819767474518</v>
+      </c>
+      <c r="AL16">
+        <v>1.967001948418911</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <v>-1.0266258022456951</v>
+      </c>
+      <c r="C17">
+        <v>-0.64093779146933427</v>
+      </c>
+      <c r="D17">
+        <v>-1.322189122127466</v>
+      </c>
+      <c r="E17">
+        <v>-1.0360550345140871</v>
+      </c>
+      <c r="F17">
+        <v>-1.0492612412804709</v>
+      </c>
+      <c r="G17">
+        <v>-0.91522010215562155</v>
+      </c>
+      <c r="H17">
+        <v>-1.026386016517346</v>
+      </c>
+      <c r="I17">
+        <v>-0.74576863866770371</v>
+      </c>
+      <c r="J17">
+        <v>-0.62535225751907175</v>
+      </c>
+      <c r="K17">
+        <v>-0.94320757460853766</v>
+      </c>
+      <c r="L17">
+        <v>-0.6859599528443</v>
+      </c>
+      <c r="M17">
+        <v>-0.44273266833996072</v>
+      </c>
+      <c r="N17">
+        <v>-0.87801628635223938</v>
+      </c>
+      <c r="O17">
+        <v>-0.79650959617593442</v>
+      </c>
+      <c r="P17">
+        <v>-0.53274231995468158</v>
+      </c>
+      <c r="Q17">
+        <v>-0.86052937703520893</v>
+      </c>
+      <c r="R17">
+        <v>-0.82194133455360197</v>
+      </c>
+      <c r="S17">
+        <v>-0.69916261179334638</v>
+      </c>
+      <c r="T17">
+        <v>-0.37867426199465271</v>
+      </c>
+      <c r="U17">
+        <v>-0.7820899828851513</v>
+      </c>
+      <c r="V17">
+        <v>-0.72072269075084006</v>
+      </c>
+      <c r="W17">
+        <v>-0.62813167671142589</v>
+      </c>
+      <c r="X17">
+        <v>-0.86800115881863416</v>
+      </c>
+      <c r="Y17">
+        <v>-0.73150800983552533</v>
+      </c>
+      <c r="Z17">
+        <v>-0.5475204879297263</v>
+      </c>
+      <c r="AA17">
+        <v>-0.71720013820314232</v>
+      </c>
+      <c r="AB17">
+        <v>-0.97672091182412479</v>
+      </c>
+      <c r="AC17">
+        <v>-0.90450547249988178</v>
+      </c>
+      <c r="AD17">
+        <v>-0.97172853319063435</v>
+      </c>
+      <c r="AE17">
+        <v>-0.8760521471292908</v>
+      </c>
+      <c r="AF17">
+        <v>-0.41078501943936863</v>
+      </c>
+      <c r="AG17">
+        <v>-0.86796378309706934</v>
+      </c>
+      <c r="AH17">
+        <v>-1.0190096529235471</v>
+      </c>
+      <c r="AI17">
+        <v>-0.72101240412916601</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.86765734694186081</v>
+      </c>
+      <c r="AK17">
+        <v>-0.6658320298170961</v>
+      </c>
+      <c r="AL17">
+        <v>-1.22672904380676</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18">
+        <v>151.96770819868311</v>
+      </c>
+      <c r="C18">
+        <v>152.77882608097761</v>
+      </c>
+      <c r="D18">
+        <v>148.65880674537141</v>
+      </c>
+      <c r="E18">
+        <v>148.89252771952101</v>
+      </c>
+      <c r="F18">
+        <v>148.31002762138209</v>
+      </c>
+      <c r="G18">
+        <v>149.44340139635369</v>
+      </c>
+      <c r="H18">
+        <v>148.51676800577931</v>
+      </c>
+      <c r="I18">
+        <v>147.53011172319671</v>
+      </c>
+      <c r="J18">
+        <v>146.8844725720848</v>
+      </c>
+      <c r="K18">
+        <v>146.34545669434459</v>
+      </c>
+      <c r="L18">
+        <v>148.706321950974</v>
+      </c>
+      <c r="M18">
+        <v>148.21809890256841</v>
+      </c>
+      <c r="N18">
+        <v>149.57883795327999</v>
+      </c>
+      <c r="O18">
+        <v>146.62030655242381</v>
+      </c>
+      <c r="P18">
+        <v>148.04759309790529</v>
+      </c>
+      <c r="Q18">
+        <v>148.51434254063551</v>
+      </c>
+      <c r="R18">
+        <v>147.9713212129692</v>
+      </c>
+      <c r="S18">
+        <v>147.46049182064161</v>
+      </c>
+      <c r="T18">
+        <v>147.1268672906393</v>
+      </c>
+      <c r="U18">
+        <v>147.48074326972539</v>
+      </c>
+      <c r="V18">
+        <v>147.2407399314655</v>
+      </c>
+      <c r="W18">
+        <v>149.82550256443301</v>
+      </c>
+      <c r="X18">
+        <v>149.44298541879439</v>
+      </c>
+      <c r="Y18">
+        <v>148.54949526960829</v>
+      </c>
+      <c r="Z18">
+        <v>149.51538468492791</v>
+      </c>
+      <c r="AA18">
+        <v>148.01455553000781</v>
+      </c>
+      <c r="AB18">
+        <v>147.99855152837381</v>
+      </c>
+      <c r="AC18">
+        <v>149.21523473286359</v>
+      </c>
+      <c r="AD18">
+        <v>148.0598114075346</v>
+      </c>
+      <c r="AE18">
+        <v>146.3629524670126</v>
+      </c>
+      <c r="AF18">
+        <v>148.187624229243</v>
+      </c>
+      <c r="AG18">
+        <v>152.48934107593311</v>
+      </c>
+      <c r="AH18">
+        <v>149.79427260778399</v>
+      </c>
+      <c r="AI18">
+        <v>149.17494360584951</v>
+      </c>
+      <c r="AJ18">
+        <v>150.80298518557549</v>
+      </c>
+      <c r="AK18">
+        <v>153.91519049418531</v>
+      </c>
+      <c r="AL18">
+        <v>149.90408139044061</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19">
+        <v>2170491.54</v>
+      </c>
+      <c r="C19">
+        <v>2336255.63</v>
+      </c>
+      <c r="D19">
+        <v>2088692.98</v>
+      </c>
+      <c r="E19">
+        <v>2601971.37</v>
+      </c>
+      <c r="F19">
+        <v>3116958.08</v>
+      </c>
+      <c r="G19">
+        <v>2635612.17</v>
+      </c>
+      <c r="H19">
+        <v>2901557.86</v>
+      </c>
+      <c r="I19">
+        <v>3455329.99</v>
+      </c>
+      <c r="J19">
+        <v>5476733.5700000003</v>
+      </c>
+      <c r="K19">
+        <v>3802468.45</v>
+      </c>
+      <c r="L19">
+        <v>4734248.33</v>
+      </c>
+      <c r="M19">
+        <v>4250097.5</v>
+      </c>
+      <c r="N19">
+        <v>3943072.03</v>
+      </c>
+      <c r="O19">
+        <v>3722125.38</v>
+      </c>
+      <c r="P19">
+        <v>2644270.5299999998</v>
+      </c>
+      <c r="Q19">
+        <v>3819553.41</v>
+      </c>
+      <c r="R19">
+        <v>3133316.48</v>
+      </c>
+      <c r="S19">
+        <v>3895067.43</v>
+      </c>
+      <c r="T19">
+        <v>3003857.99</v>
+      </c>
+      <c r="U19">
+        <v>2675898.64</v>
+      </c>
+      <c r="V19">
+        <v>2959204.94</v>
+      </c>
+      <c r="W19">
+        <v>2810813.97</v>
+      </c>
+      <c r="X19">
+        <v>2676605.2200000002</v>
+      </c>
+      <c r="Y19">
+        <v>2295872.36</v>
+      </c>
+      <c r="Z19">
+        <v>2292685.04</v>
+      </c>
+      <c r="AA19">
+        <v>2239254.39</v>
+      </c>
+      <c r="AB19">
+        <v>1539259.12</v>
+      </c>
+      <c r="AC19">
+        <v>1695626.35</v>
+      </c>
+      <c r="AD19">
+        <v>1710063.05</v>
+      </c>
+      <c r="AE19">
+        <v>1784651.26</v>
+      </c>
+      <c r="AF19">
+        <v>1638424.93</v>
+      </c>
+      <c r="AG19">
+        <v>1464431.68</v>
+      </c>
+      <c r="AH19">
+        <v>1459389.99</v>
+      </c>
+      <c r="AI19">
+        <v>1148261.18</v>
+      </c>
+      <c r="AJ19">
+        <v>1628761.97</v>
+      </c>
+      <c r="AK19">
+        <v>1061192.51</v>
+      </c>
+      <c r="AL19">
+        <v>534762.20000000007</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
+        <v>1.4359793276640269</v>
+      </c>
+      <c r="C20">
+        <v>1.4207757092708331</v>
+      </c>
+      <c r="D20">
+        <v>1.5627109036881219</v>
+      </c>
+      <c r="E20">
+        <v>1.618883534436566</v>
+      </c>
+      <c r="F20">
+        <v>1.5983887941036441</v>
+      </c>
+      <c r="G20">
+        <v>1.605346675303025</v>
+      </c>
+      <c r="H20">
+        <v>1.6660758291398301</v>
+      </c>
+      <c r="I20">
+        <v>1.683937959734322</v>
+      </c>
+      <c r="J20">
+        <v>1.623868350694726</v>
+      </c>
+      <c r="K20">
+        <v>1.61933371315674</v>
+      </c>
+      <c r="L20">
+        <v>1.598861118814864</v>
+      </c>
+      <c r="M20">
+        <v>1.622251407382709</v>
+      </c>
+      <c r="N20">
+        <v>1.6111968143770909</v>
+      </c>
+      <c r="O20">
+        <v>1.670267156346835</v>
+      </c>
+      <c r="P20">
+        <v>1.592401606067648</v>
+      </c>
+      <c r="Q20">
+        <v>1.592310970281446</v>
+      </c>
+      <c r="R20">
+        <v>1.675666183632917</v>
+      </c>
+      <c r="S20">
+        <v>1.643111228048642</v>
+      </c>
+      <c r="T20">
+        <v>1.735812572075319</v>
+      </c>
+      <c r="U20">
+        <v>1.716244850768665</v>
+      </c>
+      <c r="V20">
+        <v>1.690243803766075</v>
+      </c>
+      <c r="W20">
+        <v>1.602899417239112</v>
+      </c>
+      <c r="X20">
+        <v>1.650383999925354</v>
+      </c>
+      <c r="Y20">
+        <v>1.581568061909675</v>
+      </c>
+      <c r="Z20">
+        <v>1.6678542923119981</v>
+      </c>
+      <c r="AA20">
+        <v>1.6291515139637249</v>
+      </c>
+      <c r="AB20">
+        <v>1.6022843639409139</v>
+      </c>
+      <c r="AC20">
+        <v>1.663972407859154</v>
+      </c>
+      <c r="AD20">
+        <v>1.7061942146071989</v>
+      </c>
+      <c r="AE20">
+        <v>1.7577905898959469</v>
+      </c>
+      <c r="AF20">
+        <v>1.72548109885669</v>
+      </c>
+      <c r="AG20">
+        <v>1.5491855639212579</v>
+      </c>
+      <c r="AH20">
+        <v>1.5586194512022069</v>
+      </c>
+      <c r="AI20">
+        <v>1.6800022184406089</v>
+      </c>
+      <c r="AJ20">
+        <v>1.7174389254877851</v>
+      </c>
+      <c r="AK20">
+        <v>1.6830753777471199</v>
+      </c>
+      <c r="AL20">
+        <v>1.7388093326341021</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21">
+        <v>0.26466608288922422</v>
+      </c>
+      <c r="C21">
+        <v>0.25915625416384758</v>
+      </c>
+      <c r="D21">
+        <v>0.26888841603039237</v>
+      </c>
+      <c r="E21">
+        <v>0.2648007862073441</v>
+      </c>
+      <c r="F21">
+        <v>0.26498944630400673</v>
+      </c>
+      <c r="G21">
+        <v>0.26307457288793751</v>
+      </c>
+      <c r="H21">
+        <v>0.26466265737881922</v>
+      </c>
+      <c r="I21">
+        <v>0.26065383769525291</v>
+      </c>
+      <c r="J21">
+        <v>0.25893360367884388</v>
+      </c>
+      <c r="K21">
+        <v>0.26347439392297911</v>
+      </c>
+      <c r="L21">
+        <v>0.25979942789777571</v>
+      </c>
+      <c r="M21">
+        <v>0.25632475240485658</v>
+      </c>
+      <c r="N21">
+        <v>0.26254308980503199</v>
+      </c>
+      <c r="O21">
+        <v>0.26137870851679912</v>
+      </c>
+      <c r="P21">
+        <v>0.25761060457078122</v>
+      </c>
+      <c r="Q21">
+        <v>0.2622932768147887</v>
+      </c>
+      <c r="R21">
+        <v>0.26174201906505151</v>
+      </c>
+      <c r="S21">
+        <v>0.25998803731133352</v>
+      </c>
+      <c r="T21">
+        <v>0.25540963231420932</v>
+      </c>
+      <c r="U21">
+        <v>0.26117271404121639</v>
+      </c>
+      <c r="V21">
+        <v>0.26029603843929772</v>
+      </c>
+      <c r="W21">
+        <v>0.25897330966730608</v>
+      </c>
+      <c r="X21">
+        <v>0.26240001655455192</v>
+      </c>
+      <c r="Y21">
+        <v>0.26045011442622179</v>
+      </c>
+      <c r="Z21">
+        <v>0.25782172125613889</v>
+      </c>
+      <c r="AA21">
+        <v>0.26024571626004489</v>
+      </c>
+      <c r="AB21">
+        <v>0.26395315588320178</v>
+      </c>
+      <c r="AC21">
+        <v>0.26292150674999831</v>
+      </c>
+      <c r="AD21">
+        <v>0.26388183618843758</v>
+      </c>
+      <c r="AE21">
+        <v>0.26251503067327558</v>
+      </c>
+      <c r="AF21">
+        <v>0.25586835742056241</v>
+      </c>
+      <c r="AG21">
+        <v>0.26239948261567242</v>
+      </c>
+      <c r="AH21">
+        <v>0.26455728075605067</v>
+      </c>
+      <c r="AI21">
+        <v>0.26030017720184517</v>
+      </c>
+      <c r="AJ21">
+        <v>0.2623951049563123</v>
+      </c>
+      <c r="AK21">
+        <v>0.25951188614024417</v>
+      </c>
+      <c r="AL21">
+        <v>0.26752470062581091</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>